--- a/output/tables/parental dominance interactions.xlsx
+++ b/output/tables/parental dominance interactions.xlsx
@@ -1,21 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0. github PROJECTS\narc and intergenerational assistance\output\tables\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D92A4D-DAFF-43AA-8E3D-25AA6D014BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="25">
+  <si>
+    <t>wave</t>
+  </si>
+  <si>
+    <t>outcome</t>
+  </si>
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>sig</t>
+  </si>
+  <si>
+    <t>r2</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>w9</t>
+  </si>
+  <si>
+    <t>par</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>sex.w9Male</t>
+  </si>
+  <si>
+    <t>adm.w9</t>
+  </si>
+  <si>
+    <t>riv.w9</t>
+  </si>
+  <si>
+    <t>sex.w9Male:adm.w9</t>
+  </si>
+  <si>
+    <t>sex.w9Male:riv.w9</t>
+  </si>
+  <si>
+    <t>moth</t>
+  </si>
+  <si>
+    <t>fath</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>w11</t>
+  </si>
+  <si>
+    <t>adm.w11</t>
+  </si>
+  <si>
+    <t>riv.w11</t>
+  </si>
+  <si>
+    <t>sex.w9Male:adm.w11</t>
+  </si>
+  <si>
+    <t>sex.w9Male:riv.w11</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -59,17 +145,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office 2007–2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +201,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office 2007–2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +235,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +270,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office 2007–2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,127 +446,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="27.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>wave</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>outcome</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>beta</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sig</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>r2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H2">
         <v>3531</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sex.w9Male</t>
-        </is>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
       </c>
       <c r="D3">
         <v>-0.06</v>
       </c>
       <c r="E3">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="G3">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H3">
         <v>3531</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>adm.w9</t>
-        </is>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
       </c>
       <c r="D4">
         <v>-0.01</v>
@@ -479,27 +542,21 @@
         <v>0.622</v>
       </c>
       <c r="G4">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H4">
         <v>3531</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>riv.w9</t>
-        </is>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
         <v>0.13</v>
@@ -507,180 +564,140 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F5" t="s">
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H5">
         <v>3531</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>sex.w9Male:adm.w9</t>
-        </is>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E6">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="G6">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H6">
         <v>3531</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sex.w9Male:riv.w9</t>
-        </is>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
       </c>
       <c r="D7">
         <v>-0.01</v>
       </c>
       <c r="E7">
-        <v>0.931</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="G7">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H7">
         <v>3531</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F8" t="s">
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H8">
         <v>3330</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>sex.w9Male</t>
-        </is>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>-0.07000000000000001</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="E9">
         <v>0.193</v>
       </c>
       <c r="G9">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H9">
         <v>3330</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>adm.w9</t>
-        </is>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.957</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="G10">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H10">
         <v>3330</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>riv.w9</t>
-        </is>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
       </c>
       <c r="D11">
         <v>0.12</v>
@@ -688,99 +705,77 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F11" t="s">
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H11">
         <v>3330</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>sex.w9Male:adm.w9</t>
-        </is>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
       </c>
       <c r="D12">
         <v>0.03</v>
       </c>
       <c r="E12">
-        <v>0.569</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="G12">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H12">
         <v>3330</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>sex.w9Male:riv.w9</t>
-        </is>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
       </c>
       <c r="D13">
         <v>0.01</v>
       </c>
       <c r="E13">
-        <v>0.917</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="G13">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H13">
         <v>3330</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F14" t="s">
+        <v>11</v>
       </c>
       <c r="G14">
         <v>0.02</v>
@@ -789,21 +784,15 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>sex.w9Male</t>
-        </is>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
       </c>
       <c r="D15">
         <v>-0.09</v>
@@ -818,21 +807,15 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>adm.w9</t>
-        </is>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
       </c>
       <c r="D16">
         <v>-0.04</v>
@@ -847,32 +830,24 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>riv.w9</t>
-        </is>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
       </c>
       <c r="D17">
         <v>0.11</v>
       </c>
       <c r="E17">
-        <v>0.001</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+        <v>1E-3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
       </c>
       <c r="G17">
         <v>0.02</v>
@@ -881,32 +856,24 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>sex.w9Male:adm.w9</t>
-        </is>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
       </c>
       <c r="D18">
         <v>0.17</v>
       </c>
       <c r="E18">
-        <v>0.007</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>19</v>
       </c>
       <c r="G18">
         <v>0.02</v>
@@ -915,27 +882,21 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>w9</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>sex.w9Male:riv.w9</t>
-        </is>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
       </c>
       <c r="D19">
         <v>-0.02</v>
       </c>
       <c r="E19">
-        <v>0.732</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="G19">
         <v>0.02</v>
@@ -944,262 +905,202 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F20" t="s">
+        <v>11</v>
       </c>
       <c r="G20">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H20">
         <v>3478</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>sex.w9Male</t>
-        </is>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
       </c>
       <c r="D21">
         <v>-0.02</v>
       </c>
       <c r="E21">
-        <v>0.6860000000000001</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="G21">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H21">
         <v>3478</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>adm.w11</t>
-        </is>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
       </c>
       <c r="D22">
         <v>0.04</v>
       </c>
       <c r="E22">
-        <v>0.172</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="G22">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H22">
         <v>3478</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>riv.w11</t>
-        </is>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
       </c>
       <c r="D23">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F23" t="s">
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H23">
         <v>3478</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>sex.w9Male:adm.w11</t>
-        </is>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
       </c>
       <c r="D24">
         <v>-0.02</v>
       </c>
       <c r="E24">
-        <v>0.6820000000000001</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="G24">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H24">
         <v>3478</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>par</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>sex.w9Male:riv.w11</t>
-        </is>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
       </c>
       <c r="D25">
         <v>0.01</v>
       </c>
       <c r="E25">
-        <v>0.9330000000000001</v>
+        <v>0.93300000000000005</v>
       </c>
       <c r="G25">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H25">
         <v>3478</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F26" t="s">
+        <v>11</v>
       </c>
       <c r="G26">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H26">
         <v>3274</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>sex.w9Male</t>
-        </is>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
       </c>
       <c r="D27">
         <v>-0.03</v>
       </c>
       <c r="E27">
-        <v>0.525</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="G27">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H27">
         <v>3274</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>adm.w11</t>
-        </is>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
       </c>
       <c r="D28">
         <v>0.04</v>
@@ -1208,27 +1109,21 @@
         <v>0.129</v>
       </c>
       <c r="G28">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H28">
         <v>3274</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>riv.w11</t>
-        </is>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
       </c>
       <c r="D29">
         <v>0.13</v>
@@ -1236,62 +1131,48 @@
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F29" t="s">
+        <v>11</v>
       </c>
       <c r="G29">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H29">
         <v>3274</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>sex.w9Male:adm.w11</t>
-        </is>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0.962</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="G30">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H30">
         <v>3274</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>moth</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>sex.w9Male:riv.w11</t>
-        </is>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
       </c>
       <c r="D31">
         <v>-0.03</v>
@@ -1300,58 +1181,44 @@
         <v>0.629</v>
       </c>
       <c r="G31">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H31">
         <v>3274</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F32" t="s">
+        <v>11</v>
       </c>
       <c r="G32">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="H32">
         <v>2603</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>sex.w9Male</t>
-        </is>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
       </c>
       <c r="D33">
         <v>-0.02</v>
@@ -1360,27 +1227,21 @@
         <v>0.66</v>
       </c>
       <c r="G33">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="H33">
         <v>2603</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>adm.w11</t>
-        </is>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
       </c>
       <c r="D34">
         <v>0.03</v>
@@ -1389,27 +1250,21 @@
         <v>0.44</v>
       </c>
       <c r="G34">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="H34">
         <v>2603</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>riv.w11</t>
-        </is>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
       </c>
       <c r="D35">
         <v>0.13</v>
@@ -1417,71 +1272,57 @@
       <c r="E35">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
+      <c r="F35" t="s">
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="H35">
         <v>2603</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>sex.w9Male:adm.w11</t>
-        </is>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
       </c>
       <c r="D36">
         <v>-0.03</v>
       </c>
       <c r="E36">
-        <v>0.618</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="G36">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="H36">
         <v>2603</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>w11</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>fath</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>sex.w9Male:riv.w11</t>
-        </is>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
       </c>
       <c r="D37">
         <v>0.06</v>
       </c>
       <c r="E37">
-        <v>0.369</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="G37">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="H37">
         <v>2603</v>
